--- a/www/download/IND.abstract_labour.emp.s.mv.rpO1.xlsx
+++ b/www/download/IND.abstract_labour.emp.s.mv.rpO1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18018811.291</t>
+          <t>18018811290930.7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18235591.616</t>
+          <t>18235591615683.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19030292.436</t>
+          <t>19030292435831.4</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19140722.461</t>
+          <t>19140722461424.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22485580.047</t>
+          <t>22485580047083.4</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>24961210.806</t>
+          <t>24961210805579.1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25040581.579</t>
+          <t>25040581579156.1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>26803026.979</t>
+          <t>26803026978889.6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>32563575.278</t>
+          <t>32563575278261.5</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>33242241.704</t>
+          <t>33242241703672.3</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>33059719.529</t>
+          <t>33059719529315.6</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>30828593.473</t>
+          <t>30828593472936.8</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>28062294.281</t>
+          <t>28062294280925.4</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>23311125.27</t>
+          <t>23311125270352.9</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>22268231.15</t>
+          <t>22268231150434.2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12195030.857</t>
+          <t>12195030856625.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10757759.508</t>
+          <t>10757759508277</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9987763.116</t>
+          <t>9987763115734.44</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>11512879.391</t>
+          <t>11512879391494.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>12414320.057</t>
+          <t>12414320057144.5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>12912784.679</t>
+          <t>12912784678764.1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13696114.984</t>
+          <t>13696114984234.9</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14226855.738</t>
+          <t>14226855738280.8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>16623598.341</t>
+          <t>16623598340725.4</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>15701869.301</t>
+          <t>15701869301148.2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>14626180.824</t>
+          <t>14626180823878.4</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>13327602.77</t>
+          <t>13327602769572.5</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>11464577.955</t>
+          <t>11464577954665.3</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>9790487.824</t>
+          <t>9790487824452.34</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>9064397.164</t>
+          <t>9064397164214.81</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14049633.337</t>
+          <t>14049633336652.3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12321735.904</t>
+          <t>12321735904159.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11659651.799</t>
+          <t>11659651799369.5</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>13373723.681</t>
+          <t>13373723681264.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>14640105.669</t>
+          <t>14640105668593.3</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>15326588.459</t>
+          <t>15326588458964.2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>16848463.869</t>
+          <t>16848463869346.8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17768923.144</t>
+          <t>17768923144258.8</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>20713787.76</t>
+          <t>20713787759855.2</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>19677648.838</t>
+          <t>19677648838184.7</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>18209988.843</t>
+          <t>18209988843057.3</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>16594298.568</t>
+          <t>16594298567781.6</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>14339417.919</t>
+          <t>14339417918514.1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>12193222.145</t>
+          <t>12193222144905</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>11445309.819</t>
+          <t>11445309819029.4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>538354.752</t>
+          <t>538354752307.838</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>458933.409</t>
+          <t>458933409425.92</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>372427.2</t>
+          <t>372427200436.653</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>547887.366</t>
+          <t>547887365850.213</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>574692.567</t>
+          <t>574692566782.437</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>604350.813</t>
+          <t>604350813094.718</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>702194.276</t>
+          <t>702194275808.698</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>756796.821</t>
+          <t>756796821122.546</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>946148.175</t>
+          <t>946148175109.407</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>957267.092</t>
+          <t>957267092155.428</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>947542.283</t>
+          <t>947542282633.035</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>911145.065</t>
+          <t>911145065085.598</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>896084.98</t>
+          <t>896084980478.915</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>870273.039</t>
+          <t>870273038877.905</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>879275.644</t>
+          <t>879275643504.779</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>29124900.468</t>
+          <t>29124900467845.6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>28512144.172</t>
+          <t>28512144172205</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>29716643.829</t>
+          <t>29716643828547</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>32755591.894</t>
+          <t>32755591894338.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>24354788.347</t>
+          <t>24354788347240</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30680381.206</t>
+          <t>30680381206161.2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>28402230.689</t>
+          <t>28402230688715.2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>25222326.379</t>
+          <t>25222326379323.5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>25304829.623</t>
+          <t>25304829623429.6</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>25199020.831</t>
+          <t>25199020830851.5</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>30837261.915</t>
+          <t>30837261914676</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>33592610.297</t>
+          <t>33592610296933.8</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>37119590.143</t>
+          <t>37119590142901</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>33525023.513</t>
+          <t>33525023513290.7</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>33218320.503</t>
+          <t>33218320502691.2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>26193242.067</t>
+          <t>26193242066526.5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>24547797.611</t>
+          <t>24547797611039</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>26768137.443</t>
+          <t>26768137442925.2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29636894.269</t>
+          <t>29636894269442.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>33984812.105</t>
+          <t>33984812104557.4</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>42629639.208</t>
+          <t>42629639208214.3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>45807978.529</t>
+          <t>45807978528901.3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>45322918.061</t>
+          <t>45322918061459.7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>50884884.946</t>
+          <t>50884884946300.1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>48650429.579</t>
+          <t>48650429579254.3</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>49416542.976</t>
+          <t>49416542975837</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>48492337.819</t>
+          <t>48492337818988.3</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>40595211.08</t>
+          <t>40595211080228</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>32488595.428</t>
+          <t>32488595428413.3</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>28219665.164</t>
+          <t>28219665163816</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>32415888.798</t>
+          <t>32415888797866.3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>34525608.397</t>
+          <t>34525608397353.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>40029940.956</t>
+          <t>40029940956233.2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>47491621.468</t>
+          <t>47491621467521.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>53677184.387</t>
+          <t>53677184386803.1</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>66984731.26</t>
+          <t>66984731259699.7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>78050378.828</t>
+          <t>78050378827657.8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>80771817.714</t>
+          <t>80771817714119.7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>84790591.13</t>
+          <t>84790591130037.8</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>82600060.328</t>
+          <t>82600060327921</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>83777903.18</t>
+          <t>83777903180301.4</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>83887839.68</t>
+          <t>83887839680380</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>78448084.465</t>
+          <t>78448084464975.9</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>76361494.745</t>
+          <t>76361494745393.2</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>81932576.411</t>
+          <t>81932576410637</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>430596.215</t>
+          <t>430596215158.732</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>400733.803</t>
+          <t>400733803282.576</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>409047.771</t>
+          <t>409047770697.803</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>480004.349</t>
+          <t>480004349334.062</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>532949.586</t>
+          <t>532949586130.666</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>582967.167</t>
+          <t>582967167496.915</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>648761.709</t>
+          <t>648761709433.087</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>701553.76</t>
+          <t>701553759736.531</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>874622.96</t>
+          <t>874622960166.689</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>866417.725</t>
+          <t>866417724608.284</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>836584.535</t>
+          <t>836584534905.798</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>773880.694</t>
+          <t>773880694395.06</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>666930.888</t>
+          <t>666930887627.291</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>579722.526</t>
+          <t>579722526433.309</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>542208.509</t>
+          <t>542208508993.083</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1774220.265</t>
+          <t>1774220264595.37</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2408689.642</t>
+          <t>2408689642074.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2380884.652</t>
+          <t>2380884652266.79</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2806375.086</t>
+          <t>2806375085743.31</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2946613.449</t>
+          <t>2946613448691.55</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3254870.131</t>
+          <t>3254870130726.53</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3857178.927</t>
+          <t>3857178926548.14</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4695950.884</t>
+          <t>4695950883706.3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>5579213.602</t>
+          <t>5579213602196.61</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5442919.781</t>
+          <t>5442919780502.1</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>5526957.622</t>
+          <t>5526957622397.52</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>5460306.548</t>
+          <t>5460306548101.46</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>4999248.878</t>
+          <t>4999248877730.45</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>4803211.668</t>
+          <t>4803211668282.54</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>4079918.089</t>
+          <t>4079918088876.92</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>126938171.469</t>
+          <t>126938171468818</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>110901445.198</t>
+          <t>110901445197760</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>102240899.854</t>
+          <t>102240899854325</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>116103836.219</t>
+          <t>116103836219146</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>123983687.885</t>
+          <t>123983687885120</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>129204028.227</t>
+          <t>129204028227450</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>137154038.95</t>
+          <t>137154038950001</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>140410479.424</t>
+          <t>140410479423764</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>161427482.346</t>
+          <t>161427482346324</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>150403172.746</t>
+          <t>150403172746298</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>134721135.238</t>
+          <t>134721135237733</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>119019120.287</t>
+          <t>119019120286867</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>100186975.88</t>
+          <t>100186975879714</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>84028811.106</t>
+          <t>84028811106481.5</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>79177717.599</t>
+          <t>79177717598898.7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>8442586.072</t>
+          <t>8442586071671.95</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7785704.424</t>
+          <t>7785704423646.29</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7509188.949</t>
+          <t>7509188948864.92</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>8826323.347</t>
+          <t>8826323347103.51</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>9635620.229</t>
+          <t>9635620229377.81</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>10075044.892</t>
+          <t>10075044892031.3</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>11017656.449</t>
+          <t>11017656448816.5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>11674526.927</t>
+          <t>11674526926908.9</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>13702573.455</t>
+          <t>13702573454559.9</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>13003070.065</t>
+          <t>13003070065212.2</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>12180157.372</t>
+          <t>12180157372035</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>11186947.995</t>
+          <t>11186947994748</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>9769135.056</t>
+          <t>9769135055943.88</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>8264869.097</t>
+          <t>8264869096848.15</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>7716603.274</t>
+          <t>7716603274220.85</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>29175353.133</t>
+          <t>29175353133075.8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>27483837.796</t>
+          <t>27483837796133.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>26619141.686</t>
+          <t>26619141685687.8</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>31371144.542</t>
+          <t>31371144541604</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>34845035.142</t>
+          <t>34845035141615.2</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>37346551.678</t>
+          <t>37346551678469.6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>41687749.755</t>
+          <t>41687749754791.7</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>44827740.551</t>
+          <t>44827740550566.1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>54352250.375</t>
+          <t>54352250374687.8</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>53132111.066</t>
+          <t>53132111065561.7</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>51003076.859</t>
+          <t>51003076858716.5</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>47763990.145</t>
+          <t>47763990145198.4</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>42343328.676</t>
+          <t>42343328675946</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>36161840.907</t>
+          <t>36161840907474.5</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>32798617.707</t>
+          <t>32798617706537.5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>176249.715</t>
+          <t>176249715214.328</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>191811.981</t>
+          <t>191811981146.82</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>208422.781</t>
+          <t>208422781034.85</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>258424.784</t>
+          <t>258424784080.109</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>278395.641</t>
+          <t>278395641441.636</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>316624.153</t>
+          <t>316624153029.313</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>361118.758</t>
+          <t>361118758293.202</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>407627.11</t>
+          <t>407627109870.78</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>531742.671</t>
+          <t>531742670611.337</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>556267.793</t>
+          <t>556267792943.823</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>556093.491</t>
+          <t>556093491106.798</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>583701.823</t>
+          <t>583701822650.246</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>597816.376</t>
+          <t>597816376170.093</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>547112.581</t>
+          <t>547112580960.833</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>447464.324</t>
+          <t>447464324433.542</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6236909.303</t>
+          <t>6236909303307.93</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5604702.401</t>
+          <t>5604702401307.66</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5489960.591</t>
+          <t>5489960590935.31</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>6402270.809</t>
+          <t>6402270808755.88</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6994596.62</t>
+          <t>6994596620353.25</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7424707.353</t>
+          <t>7424707353338.1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8176914.182</t>
+          <t>8176914181911.65</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8551637.465</t>
+          <t>8551637465371.46</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>10029279.693</t>
+          <t>10029279692951.6</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>9655992.403</t>
+          <t>9655992403214.04</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>9102311.889</t>
+          <t>9102311889266.71</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>8292299.193</t>
+          <t>8292299192749.7</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>7209903.793</t>
+          <t>7209903792666.51</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>6199809.417</t>
+          <t>6199809416917.8</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>5705529.185</t>
+          <t>5705529184872.06</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>72860033.945</t>
+          <t>72860033944651.9</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>65895544.45</t>
+          <t>65895544449815</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>62164567.177</t>
+          <t>62164567177389.3</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>71692574.614</t>
+          <t>71692574614273.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>77881669.681</t>
+          <t>77881669680593.4</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>82200706.187</t>
+          <t>82200706186660.4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>89390019.84</t>
+          <t>89390019840003.9</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>94748208.082</t>
+          <t>94748208081719.7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>111527319.726</t>
+          <t>111527319726138</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>106846639.344</t>
+          <t>106846639343551</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>99379519.874</t>
+          <t>99379519873754.8</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>90319300.111</t>
+          <t>90319300110708.6</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>77178211.206</t>
+          <t>77178211205501.4</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>64400535.336</t>
+          <t>64400535335501</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>59733656.311</t>
+          <t>59733656310939.5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>57429599.716</t>
+          <t>57429599716383.7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>53829383.813</t>
+          <t>53829383813310.9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>62724831.005</t>
+          <t>62724831004511.3</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>77051879.776</t>
+          <t>77051879776253.1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>86890819.215</t>
+          <t>86890819214967.5</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>100765769.381</t>
+          <t>100765769381218</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>109072598.271</t>
+          <t>109072598270824</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>114482257.81</t>
+          <t>114482257810270</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>126122683.432</t>
+          <t>126122683432007</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>125069336.713</t>
+          <t>125069336713172</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>117320454.809</t>
+          <t>117320454809254</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>108052735.454</t>
+          <t>108052735453782</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>93541825.678</t>
+          <t>93541825678335.5</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>66428094.3</t>
+          <t>66428094300199.9</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>55560473.06</t>
+          <t>55560473060145</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4873320.264</t>
+          <t>4873320264106.61</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4629393.439</t>
+          <t>4629393438993.53</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4834562.263</t>
+          <t>4834562263252.34</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>5570810.93</t>
+          <t>5570810929804.24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>6455768.143</t>
+          <t>6455768142708.96</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6718291.066</t>
+          <t>6718291066264.76</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>7319311.603</t>
+          <t>7319311602678.65</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8553076.869</t>
+          <t>8553076868889.88</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>10696914.109</t>
+          <t>10696914108758.3</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>10628311.866</t>
+          <t>10628311866129.4</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>10112394.261</t>
+          <t>10112394260618.9</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>9513888.897</t>
+          <t>9513888897034.34</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>8400829.747</t>
+          <t>8400829747124.31</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>7232193.485</t>
+          <t>7232193484896.28</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>6979065.611</t>
+          <t>6979065611090.48</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2034609.715</t>
+          <t>2034609715237.83</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1827089.296</t>
+          <t>1827089295517.74</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1931779.596</t>
+          <t>1931779595577.48</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2206594.251</t>
+          <t>2206594251127.53</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2359332.904</t>
+          <t>2359332904026.24</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2797644.451</t>
+          <t>2797644450712.7</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3266956.619</t>
+          <t>3266956618929.02</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3981909.587</t>
+          <t>3981909587458.89</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>4831895.181</t>
+          <t>4831895180801.91</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4921050.109</t>
+          <t>4921050108578.29</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>4791441.489</t>
+          <t>4791441489054.26</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4154325.103</t>
+          <t>4154325102615.51</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>3814945.216</t>
+          <t>3814945215610.9</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3230660.555</t>
+          <t>3230660555311.95</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2584947.356</t>
+          <t>2584947355624.93</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9957952.989</t>
+          <t>9957952988531.38</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10270678.023</t>
+          <t>10270678022847.4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10673698.771</t>
+          <t>10673698771235.6</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>4891603.386</t>
+          <t>4891603385535.45</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>8043650.083</t>
+          <t>8043650082641.22</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>9595683.207</t>
+          <t>9595683207327.28</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>9730175.892</t>
+          <t>9730175891704.46</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>11256768.829</t>
+          <t>11256768828603</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>13239068.81</t>
+          <t>13239068809871.1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>11377012.71</t>
+          <t>11377012709707.3</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>10668434.542</t>
+          <t>10668434542302.8</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>11960413.204</t>
+          <t>11960413203516</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>10764865.239</t>
+          <t>10764865238712.1</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>9412089.447</t>
+          <t>9412089447083.56</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>9786296.76</t>
+          <t>9786296759667.64</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16139586.085</t>
+          <t>16139586085320.5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>14479861.687</t>
+          <t>14479861687263.6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17180086.511</t>
+          <t>17180086511284.1</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>19189622.513</t>
+          <t>19189622513459.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>21773594.799</t>
+          <t>21773594798737.2</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>26082596.044</t>
+          <t>26082596043994.6</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>29263528.85</t>
+          <t>29263528849724.3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>29358938.424</t>
+          <t>29358938424040.5</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>32714374.878</t>
+          <t>32714374878065.4</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>31902177.964</t>
+          <t>31902177963662</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>33286370.706</t>
+          <t>33286370706307.7</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>32221183.939</t>
+          <t>32221183938755</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>30298367.565</t>
+          <t>30298367564980.5</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>24753626.604</t>
+          <t>24753626604233.8</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>25266284.091</t>
+          <t>25266284090694.6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3047900.894</t>
+          <t>3047900894367.14</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2979536.189</t>
+          <t>2979536188667</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3311691.491</t>
+          <t>3311691490681.99</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>3977776.22</t>
+          <t>3977776220112.21</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>4570298.181</t>
+          <t>4570298180745.46</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5206246.149</t>
+          <t>5206246148647.55</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5996392.838</t>
+          <t>5996392838427.75</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>6540879.943</t>
+          <t>6540879942642.85</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>8068361.845</t>
+          <t>8068361844613.56</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>8117391.271</t>
+          <t>8117391271409.42</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>8094800.95</t>
+          <t>8094800950246.81</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>7718767.554</t>
+          <t>7718767553944.3</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>6949068.655</t>
+          <t>6949068655221.09</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>5943290.661</t>
+          <t>5943290661207.7</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>5015700.257</t>
+          <t>5015700257171.28</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>55382248.887</t>
+          <t>55382248886711.7</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>55984786.471</t>
+          <t>55984786470819.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>55714709.367</t>
+          <t>55714709367156.4</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61588902.183</t>
+          <t>61588902182854.7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>66052371.981</t>
+          <t>66052371981109.8</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>68929712.87</t>
+          <t>68929712870294.9</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>75340419.758</t>
+          <t>75340419758470</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>79940987.379</t>
+          <t>79940987379468.5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>95207772.77</t>
+          <t>95207772770290.7</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>90754508.528</t>
+          <t>90754508528266.5</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>84669419.628</t>
+          <t>84669419628319.3</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>76471639.299</t>
+          <t>76471639299270.5</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>65234581.868</t>
+          <t>65234581868455.1</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>54721819.908</t>
+          <t>54721819908084.1</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>50848045.588</t>
+          <t>50848045587841.8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>257573190.974</t>
+          <t>257573190974183</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>199739641.291</t>
+          <t>199739641291349</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>191940130.515</t>
+          <t>191940130514911</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>197115642.012</t>
+          <t>197115642011997</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>240150130.976</t>
+          <t>240150130975823</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>294830699.307</t>
+          <t>294830699307283</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>277319904.884</t>
+          <t>277319904884055</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>252550226.705</t>
+          <t>252550226704897</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>257803375.987</t>
+          <t>257803375987432</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>234774449.264</t>
+          <t>234774449264408</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>208657604.147</t>
+          <t>208657604146544</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>172966888.618</t>
+          <t>172966888618248</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>130275102.025</t>
+          <t>130275102024601</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>108669039.99</t>
+          <t>108669039989617</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>108153602.261</t>
+          <t>108153602261194</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>31807441.389</t>
+          <t>31807441389028.8</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>31674921.244</t>
+          <t>31674921243973.5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>30568163.637</t>
+          <t>30568163636971.4</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>22550414.111</t>
+          <t>22550414110557.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>29734286.904</t>
+          <t>29734286903590.7</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>38988599.301</t>
+          <t>38988599300811.2</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>40245149.746</t>
+          <t>40245149746278.7</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>43644515.834</t>
+          <t>43644515833896.6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>47291309.626</t>
+          <t>47291309625656.3</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>43618209.678</t>
+          <t>43618209678247.5</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>46608793.23</t>
+          <t>46608793230312.5</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>44944259.25</t>
+          <t>44944259250404.4</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>36579167.181</t>
+          <t>36579167180978.8</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>24840875.383</t>
+          <t>24840875383241.7</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>21596521.507</t>
+          <t>21596521507293.8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>238844.167</t>
+          <t>238844167394.911</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>325763.81</t>
+          <t>325763809532.094</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>373352.532</t>
+          <t>373352531676.247</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>482663.317</t>
+          <t>482663317249.182</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>511579.03</t>
+          <t>511579030327.591</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>568967.809</t>
+          <t>568967809378.253</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>642306.06</t>
+          <t>642306059942.19</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>725681.602</t>
+          <t>725681602405.211</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>916784.962</t>
+          <t>916784961652.103</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>962338.303</t>
+          <t>962338303155.914</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>997539.351</t>
+          <t>997539351012.904</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1028221.375</t>
+          <t>1028221374970.38</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1018047.602</t>
+          <t>1018047601650.73</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>959086.218</t>
+          <t>959086218423.238</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>737917.975</t>
+          <t>737917974514.75</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>855782.682</t>
+          <t>855782681671.417</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>769702.358</t>
+          <t>769702358388.688</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>741810.494</t>
+          <t>741810494367.382</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>871138.595</t>
+          <t>871138595149.474</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>987993.023</t>
+          <t>987993022637.495</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1104799.729</t>
+          <t>1104799729481.32</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1258350.709</t>
+          <t>1258350708507.14</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1361545.548</t>
+          <t>1361545547563.43</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1605075.374</t>
+          <t>1605075374310.32</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1565692.366</t>
+          <t>1565692365517.99</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1510332.78</t>
+          <t>1510332779608.5</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1398078.789</t>
+          <t>1398078788822.1</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1244945.1</t>
+          <t>1244945099608.92</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1157045.808</t>
+          <t>1157045808302.91</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1114800.04</t>
+          <t>1114800040208.41</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>198294.547</t>
+          <t>198294547204.603</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>214912.014</t>
+          <t>214912013944.869</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>246419.374</t>
+          <t>246419374382.138</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>289176.62</t>
+          <t>289176620012.836</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>337993.135</t>
+          <t>337993134933.226</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>394047.36</t>
+          <t>394047360178.067</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>434103.081</t>
+          <t>434103080988.801</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>450993.779</t>
+          <t>450993778526.976</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>531410.526</t>
+          <t>531410526347.63</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>546467.455</t>
+          <t>546467455424.499</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>606941.767</t>
+          <t>606941767291.142</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>680022.845</t>
+          <t>680022844510.57</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>789274.488</t>
+          <t>789274487678.116</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>751432.917</t>
+          <t>751432916750.966</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>514392.921</t>
+          <t>514392921369.617</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>8821226.261</t>
+          <t>8821226260616.68</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8564506.661</t>
+          <t>8564506661416.82</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11108872.164</t>
+          <t>11108872164230.5</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>13647299.276</t>
+          <t>13647299275668.3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>17174354.372</t>
+          <t>17174354372307.2</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>24079101.398</t>
+          <t>24079101398410.2</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>28855976.088</t>
+          <t>28855976088422.8</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>29134852.226</t>
+          <t>29134852226121.1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>26604955.459</t>
+          <t>26604955458709.9</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>22911047.39</t>
+          <t>22911047390091.6</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>22785051.119</t>
+          <t>22785051118503.8</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>21259508.159</t>
+          <t>21259508158869.4</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>17098068.401</t>
+          <t>17098068400721</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>13564538.701</t>
+          <t>13564538701371</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>10799896.439</t>
+          <t>10799896438557.4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>149817.214</t>
+          <t>149817213735.506</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>144066.526</t>
+          <t>144066526448.639</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>147193.39</t>
+          <t>147193390057.884</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>174643.391</t>
+          <t>174643391025.492</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>193349.069</t>
+          <t>193349069345.177</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>214077.454</t>
+          <t>214077453968.013</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>240160.226</t>
+          <t>240160226278.626</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>253138.825</t>
+          <t>253138825484.748</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>289116.253</t>
+          <t>289116253199.535</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>277583.268</t>
+          <t>277583268150.303</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>255434.075</t>
+          <t>255434075369.334</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>235463.512</t>
+          <t>235463512360.116</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>202907.325</t>
+          <t>202907325334.163</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>192382.472</t>
+          <t>192382472034.895</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>177618.228</t>
+          <t>177618227570.444</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>20761175.374</t>
+          <t>20761175374167.9</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>18665910.506</t>
+          <t>18665910505820.1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>17897335.716</t>
+          <t>17897335715802.6</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>21134351.343</t>
+          <t>21134351342577.2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>23492110.8</t>
+          <t>23492110799582.3</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>25265834.39</t>
+          <t>25265834389960.3</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>28125380.658</t>
+          <t>28125380658080.1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>29995400.14</t>
+          <t>29995400140275.9</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>35266526.27</t>
+          <t>35266526269826.5</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>33453158.939</t>
+          <t>33453158938982.6</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>30494441.835</t>
+          <t>30494441835184.6</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>27646530.143</t>
+          <t>27646530142723.4</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>23989405.413</t>
+          <t>23989405413274.9</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>20327728.637</t>
+          <t>20327728636900.5</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>19161062.465</t>
+          <t>19161062465377.5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>9974312.18</t>
+          <t>9974312180358.17</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10065875.634</t>
+          <t>10065875634498.6</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>10764350.543</t>
+          <t>10764350542879.7</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>13838412.209</t>
+          <t>13838412209076.7</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14735342.775</t>
+          <t>14735342774898.4</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>13179120.5</t>
+          <t>13179120499952.2</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>14370000.759</t>
+          <t>14370000758932.8</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>13456896.802</t>
+          <t>13456896802345.9</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>13439165.299</t>
+          <t>13439165298544.8</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>12409292.957</t>
+          <t>12409292956701.2</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>13062644.262</t>
+          <t>13062644261774.2</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>12156282.032</t>
+          <t>12156282032339.3</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>11158029.189</t>
+          <t>11158029189138.9</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>10861414.472</t>
+          <t>10861414471635.7</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>8501806.967</t>
+          <t>8501806966688.73</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5246277.602</t>
+          <t>5246277602209.75</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5005103.558</t>
+          <t>5005103558126.36</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>5034164.495</t>
+          <t>5034164494548.32</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>6011000.399</t>
+          <t>6011000398523.3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>6682753.393</t>
+          <t>6682753393091.31</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>7263155.56</t>
+          <t>7263155560062.07</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>8002135.062</t>
+          <t>8002135062151.95</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>8481097.049</t>
+          <t>8481097048546.86</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>9953846.218</t>
+          <t>9953846218030.5</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>9468859.23</t>
+          <t>9468859229667.95</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>8870608.588</t>
+          <t>8870608587745.03</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>8081082.678</t>
+          <t>8081082678048.88</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>6918252.663</t>
+          <t>6918252662566.81</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>5761111.45</t>
+          <t>5761111449811.42</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>5341474.863</t>
+          <t>5341474862933.02</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1707254.695</t>
+          <t>1707254695272.45</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1537410.035</t>
+          <t>1537410034765.27</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1387483.751</t>
+          <t>1387483750563.31</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2238684.407</t>
+          <t>2238684407247.02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1832228.77</t>
+          <t>1832228769665.88</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2466910.681</t>
+          <t>2466910681396.42</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3189836.186</t>
+          <t>3189836185598.07</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>3336698.864</t>
+          <t>3336698863681.9</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>4146463.212</t>
+          <t>4146463212171.66</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>3470434.886</t>
+          <t>3470434886137.67</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>4665450.471</t>
+          <t>4665450471404.57</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>4969763.71</t>
+          <t>4969763710472.11</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>5041132.238</t>
+          <t>5041132238063.46</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>4815582.603</t>
+          <t>4815582602773.21</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>3600842.907</t>
+          <t>3600842906936.41</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>14876760.048</t>
+          <t>14876760048497.5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>16654839.268</t>
+          <t>16654839267508.2</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>17570438.174</t>
+          <t>17570438174322.6</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>15235255.008</t>
+          <t>15235255008147.6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>9684527.248</t>
+          <t>9684527248253.93</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>14592114.961</t>
+          <t>14592114960979.5</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>18792234.397</t>
+          <t>18792234397357.9</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>21285231.359</t>
+          <t>21285231358523.5</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>25097595.764</t>
+          <t>25097595764291.2</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>27980387.482</t>
+          <t>27980387482060</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>30961741.776</t>
+          <t>30961741776474.9</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>34638886.75</t>
+          <t>34638886749787</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>35048686.685</t>
+          <t>35048686684833.1</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>33784129.37</t>
+          <t>33784129369952.1</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>25033367.922</t>
+          <t>25033367921970.1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>534598.246</t>
+          <t>534598245811.55</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>539811.815</t>
+          <t>539811815446.099</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>608666.851</t>
+          <t>608666850574.252</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>712121.633</t>
+          <t>712121632810.749</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>686376.902</t>
+          <t>686376901997.033</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>805680.002</t>
+          <t>805680002018.74</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>868576.422</t>
+          <t>868576422199.643</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>968977.103</t>
+          <t>968977102939.703</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1247553.449</t>
+          <t>1247553449273.93</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1305628.953</t>
+          <t>1305628952887.79</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1351141.458</t>
+          <t>1351141458323.86</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>1349259.69</t>
+          <t>1349259689576.51</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1368078.502</t>
+          <t>1368078501577.8</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>1310112.423</t>
+          <t>1310112423044.78</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1258579.647</t>
+          <t>1258579647201.47</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1219263.526</t>
+          <t>1219263525686.17</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1071326.666</t>
+          <t>1071326665753.26</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1059225.752</t>
+          <t>1059225751749.17</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1231389.456</t>
+          <t>1231389456129.99</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1345924.031</t>
+          <t>1345924031215.27</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1413548.885</t>
+          <t>1413548884899.46</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1554553.193</t>
+          <t>1554553192750.18</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1677619.202</t>
+          <t>1677619202362.45</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1989826.912</t>
+          <t>1989826912017.08</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1948899.189</t>
+          <t>1948899189092.59</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1841271.732</t>
+          <t>1841271731618.61</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1709305.901</t>
+          <t>1709305901045.32</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1543595.008</t>
+          <t>1543595008091.1</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1373608.629</t>
+          <t>1373608628647.44</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1261624.849</t>
+          <t>1261624849202.98</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>11662621.967</t>
+          <t>11662621966617.2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>11924366.858</t>
+          <t>11924366858201</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>11414908.901</t>
+          <t>11414908901368.5</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>12899724.518</t>
+          <t>12899724518381.6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>13947500.942</t>
+          <t>13947500941515.8</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>16019600.191</t>
+          <t>16019600191088.5</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>16222987.377</t>
+          <t>16222987376530.5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>17113004.616</t>
+          <t>17113004615728.5</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>20247642.969</t>
+          <t>20247642968875.4</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>19340422.437</t>
+          <t>19340422437337.6</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>17710319.78</t>
+          <t>17710319779744.2</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>15999645.186</t>
+          <t>15999645185664.4</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>14148072.92</t>
+          <t>14148072919835</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>11232856.993</t>
+          <t>11232856993161.9</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>9309357.675</t>
+          <t>9309357674889.96</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5716533.681</t>
+          <t>5716533681103.94</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>6141175.742</t>
+          <t>6141175742056.26</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>7100694.035</t>
+          <t>7100694034572.07</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>8577829.294</t>
+          <t>8577829293591.09</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>10126037.242</t>
+          <t>10126037242318.4</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>11638114.557</t>
+          <t>11638114556823.6</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>9012058.63</t>
+          <t>9012058629934.64</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>9154532.481</t>
+          <t>9154532480715.78</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>11202461.948</t>
+          <t>11202461947782.4</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>12043452.133</t>
+          <t>12043452132581.5</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>13618412.601</t>
+          <t>13618412601046.6</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>12444448.657</t>
+          <t>12444448656895.8</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>11499146.928</t>
+          <t>11499146927922</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>9808048.791</t>
+          <t>9808048790823.35</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>8068959.084</t>
+          <t>8068959084055.87</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>13905947.841</t>
+          <t>13905947840746.9</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>13232369.156</t>
+          <t>13232369156054.7</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>14131665.936</t>
+          <t>14131665936167</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>14383103.071</t>
+          <t>14383103071091.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>16763795.958</t>
+          <t>16763795958255</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>20755914.824</t>
+          <t>20755914823920.9</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>20320667.791</t>
+          <t>20320667791139.6</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>19128380.219</t>
+          <t>19128380219006.1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>18821398.337</t>
+          <t>18821398337428</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>16910350.099</t>
+          <t>16910350099356.1</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>16513274.449</t>
+          <t>16513274449239.4</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>14739912.863</t>
+          <t>14739912862653.9</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>11279339.575</t>
+          <t>11279339575308.3</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>8839082.348</t>
+          <t>8839082348331.77</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>7988619.044</t>
+          <t>7988619043513.21</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>363718478.605</t>
+          <t>363718478605274</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>346079395.659</t>
+          <t>346079395658546</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>386030828.456</t>
+          <t>386030828455735</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>464684626.453</t>
+          <t>464684626453189</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>535191806.24</t>
+          <t>535191806239829</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>670036278.557</t>
+          <t>670036278556667</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>747272306.768</t>
+          <t>747272306768424</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>737640074.848</t>
+          <t>737640074847998</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>738222161.831</t>
+          <t>738222161831000</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>652651830.393</t>
+          <t>652651830393360</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>614969841.8</t>
+          <t>614969841800422</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>561598456.476</t>
+          <t>561598456476383</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>445094300.013</t>
+          <t>445094300012609</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>341760072.481</t>
+          <t>341760072481201</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>326079878.804</t>
+          <t>326079878803873</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>155827970.989</t>
+          <t>155827970988504</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>149445606.057</t>
+          <t>149445606057324</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>158517949.465</t>
+          <t>158517949465089</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>171182455.505</t>
+          <t>171182455505399</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>187786944.561</t>
+          <t>187786944560748</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>226028085.051</t>
+          <t>226028085050633</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>241892513.244</t>
+          <t>241892513244266</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>229693141.746</t>
+          <t>229693141745934</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>244493186.339</t>
+          <t>244493186338795</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>236882589.93</t>
+          <t>236882589930044</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>243764049.81</t>
+          <t>243764049810257</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>239527272.088</t>
+          <t>239527272087600</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>210680458.643</t>
+          <t>210680458642506</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>192774429.465</t>
+          <t>192774429464613</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>176069625.387</t>
+          <t>176069625386819</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1432230992.224</t>
+          <t>1432230992223992</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1315829474.09</t>
+          <t>1315829474089882</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1367601983.424</t>
+          <t>1367601983423946</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1534137394.158</t>
+          <t>1534137394158348</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1726740922.087</t>
+          <t>1726740922086799</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2054245779.906</t>
+          <t>2054245779906052</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2199449966.436</t>
+          <t>2199449966436216</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2191057216.827</t>
+          <t>2191057216827426</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2339902827.841</t>
+          <t>2339902827841108</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2181226012.109</t>
+          <t>2181226012109208</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2092369187.848</t>
+          <t>2092369187847597</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>1938500216.637</t>
+          <t>1938500216637389</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>1637857305.439</t>
+          <t>1637857305438727</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>1358030488.716</t>
+          <t>1358030488716240</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>1268040252.559</t>
+          <t>1268040252558506</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>abstract_labour.emp.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
